--- a/portal/templates/08 Config.xlsx
+++ b/portal/templates/08 Config.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="B2:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -562,40 +562,54 @@
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The split bases</t>
+          <t>Each June, before the July build</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>Add the coming year's public holidays to the Holidays tab. The portal warns on the Build page if a year in the calendar has none. Type the new year's split base percentages if the budget workbook moved them, and check the departments and users still match the org chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>The split bases</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>The 3 Way percentages are confirmed from the budget bridge. Staff and Office Dept are placeholders until the live percentages from the budget workbook are typed in. Every allocated departmental figure rests on them, and the portal flags any figure that does until they are marked Confirmed.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="5" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Cream cells with blue text: paste or type here.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="6" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Yellow cells: a setting you choose.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Grey cells: calculated or fixed. Do not type here.</t>
         </is>
@@ -2217,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2808,6 +2822,286 @@
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
+        <v>46755</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>New Year's Day</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>46778</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Australia Day</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>46825</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Labour Day</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>46857</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Good Friday</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>46860</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Easter Monday</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>46868</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Anzac Day</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>46874</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Labour Day</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n">
+        <v>46916</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>NSW</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>King's Birthday</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n">
+        <v>46916</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>King's Birthday</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n">
+        <v>47028</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>NSW</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Labour Day</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n">
+        <v>47028</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>King's Birthday</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n">
+        <v>47064</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>VIC</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Melbourne Cup</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n">
+        <v>47112</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>Christmas Day</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n">
+        <v>47113</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Boxing Day</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>

--- a/portal/templates/08 Config.xlsx
+++ b/portal/templates/08 Config.xlsx
@@ -4640,7 +4640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4970,12 +4970,12 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>rev-summary</t>
+          <t>forecast</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Revenue Summary</t>
+          <t>Forecast</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -4993,18 +4993,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>rev-schedule</t>
+          <t>rev-summary</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Revenue Schedule</t>
+          <t>Revenue Summary</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -5022,22 +5026,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F12" s="11" t="inlineStr"/>
       <c r="G12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>rev-schedule</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Revenue Schedule</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -5065,12 +5065,12 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>clients</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Top Clients</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -5098,12 +5098,12 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>client-dept</t>
+          <t>clients</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Clients by Department</t>
+          <t>Top Clients</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -5121,18 +5121,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>client-dept</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Utilisation</t>
+          <t>Clients by Department</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -5150,22 +5154,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F16" s="11" t="inlineStr"/>
       <c r="G16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>profit-fte</t>
+          <t>util</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Profitability per FTE</t>
+          <t>Utilisation</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5183,18 +5183,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>staff-profit</t>
+          <t>profit-fte</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Profitability by Employee</t>
+          <t>Profitability per FTE</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -5218,12 +5222,12 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>staff-profit</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Detail Records</t>
+          <t>Profitability by Employee</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -5236,19 +5240,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F19" s="11" t="inlineStr"/>
       <c r="G19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>charts</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Charts</t>
+          <t>Detail Records</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -5261,27 +5269,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E20" s="11" t="inlineStr"/>
+      <c r="F20" s="11" t="inlineStr"/>
       <c r="G20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>charts</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Charts</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -5294,19 +5294,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr"/>
-      <c r="F21" s="11" t="inlineStr"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>loaders</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Data Loaders</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -5326,12 +5334,12 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>loaders</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Data Loaders</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -5351,12 +5359,12 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -5376,12 +5384,12 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>config</t>
+          <t>distribution</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Config &amp; Variables</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -5401,12 +5409,12 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>access</t>
+          <t>config</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Config &amp; Variables</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -5414,7 +5422,11 @@
           <t>Always</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr"/>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E26" s="11" t="inlineStr"/>
       <c r="F26" s="11" t="inlineStr"/>
       <c r="G26" s="11" t="inlineStr"/>
@@ -5422,35 +5434,56 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr"/>
+      <c r="F27" s="11" t="inlineStr"/>
+      <c r="G27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
           <t>about</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>About</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/portal/templates/08 Config.xlsx
+++ b/portal/templates/08 Config.xlsx
@@ -4640,7 +4640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5003,12 +5003,12 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>rev-summary</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Revenue Summary</t>
+          <t>Cash Flow</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -5032,12 +5032,12 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>rev-schedule</t>
+          <t>rev-summary</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Revenue Schedule</t>
+          <t>Revenue Summary</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -5055,22 +5055,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F13" s="11" t="inlineStr"/>
       <c r="G13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>rev-schedule</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Revenue Schedule</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -5098,12 +5094,12 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>clients</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Top Clients</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -5131,12 +5127,12 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>client-dept</t>
+          <t>clients</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Clients by Department</t>
+          <t>Top Clients</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -5154,18 +5150,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr"/>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>client-dept</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Utilisation</t>
+          <t>Clients by Department</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5183,22 +5183,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F17" s="11" t="inlineStr"/>
       <c r="G17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>profit-fte</t>
+          <t>util</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Profitability per FTE</t>
+          <t>Utilisation</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -5216,18 +5212,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>staff-profit</t>
+          <t>profit-fte</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Profitability by Employee</t>
+          <t>Profitability per FTE</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -5251,12 +5251,12 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>staff-profit</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Detail Records</t>
+          <t>Profitability by Employee</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -5269,19 +5269,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr"/>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F20" s="11" t="inlineStr"/>
       <c r="G20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>charts</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Charts</t>
+          <t>Detail Records</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -5294,27 +5298,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E21" s="11" t="inlineStr"/>
+      <c r="F21" s="11" t="inlineStr"/>
       <c r="G21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>charts</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Charts</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -5327,19 +5323,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr"/>
-      <c r="F22" s="11" t="inlineStr"/>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>loaders</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Data Loaders</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -5359,12 +5363,12 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>loaders</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Data Loaders</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -5384,12 +5388,12 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -5409,12 +5413,12 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>config</t>
+          <t>distribution</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Config &amp; Variables</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -5434,12 +5438,12 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>access</t>
+          <t>config</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Config &amp; Variables</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -5447,7 +5451,11 @@
           <t>Always</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E27" s="11" t="inlineStr"/>
       <c r="F27" s="11" t="inlineStr"/>
       <c r="G27" s="11" t="inlineStr"/>
@@ -5455,35 +5463,56 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr"/>
+      <c r="E28" s="11" t="inlineStr"/>
+      <c r="F28" s="11" t="inlineStr"/>
+      <c r="G28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
           <t>about</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>About</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/portal/templates/08 Config.xlsx
+++ b/portal/templates/08 Config.xlsx
@@ -4640,7 +4640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5094,12 +5094,12 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>rev-forecast</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Revenue Forecast</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -5127,12 +5127,12 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>clients</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Top Clients</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -5160,12 +5160,12 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>client-dept</t>
+          <t>clients</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Clients by Department</t>
+          <t>Top Clients</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5183,18 +5183,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>client-dept</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Utilisation</t>
+          <t>Clients by Department</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -5212,22 +5216,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F18" s="11" t="inlineStr"/>
       <c r="G18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>profit-fte</t>
+          <t>util</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Profitability per FTE</t>
+          <t>Utilisation</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -5245,18 +5245,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>staff-profit</t>
+          <t>profit-fte</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Profitability by Employee</t>
+          <t>Profitability per FTE</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -5280,12 +5284,12 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>staff-profit</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Detail Records</t>
+          <t>Profitability by Employee</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -5298,19 +5302,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F21" s="11" t="inlineStr"/>
       <c r="G21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>charts</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Charts</t>
+          <t>Detail Records</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -5323,27 +5331,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E22" s="11" t="inlineStr"/>
+      <c r="F22" s="11" t="inlineStr"/>
       <c r="G22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>charts</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Charts</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -5356,19 +5356,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr"/>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>loaders</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Data Loaders</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -5388,12 +5396,12 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>loaders</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Data Loaders</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -5413,12 +5421,12 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -5438,12 +5446,12 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>config</t>
+          <t>distribution</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Config &amp; Variables</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -5463,12 +5471,12 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>access</t>
+          <t>config</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Config &amp; Variables</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -5476,7 +5484,11 @@
           <t>Always</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr"/>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E28" s="11" t="inlineStr"/>
       <c r="F28" s="11" t="inlineStr"/>
       <c r="G28" s="11" t="inlineStr"/>
@@ -5484,35 +5496,56 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr"/>
+      <c r="E29" s="11" t="inlineStr"/>
+      <c r="F29" s="11" t="inlineStr"/>
+      <c r="G29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
           <t>about</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>About</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/portal/templates/08 Config.xlsx
+++ b/portal/templates/08 Config.xlsx
@@ -4640,7 +4640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4771,12 +4771,12 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>pnl</t>
+          <t>commentary</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>P&amp;L</t>
+          <t>Commentary</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -4794,18 +4794,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr"/>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>pnl-dept</t>
+          <t>pnl</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>P&amp;L by Department</t>
+          <t>P&amp;L</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -4823,22 +4827,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F5" s="11" t="inlineStr"/>
       <c r="G5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>pnl-spread</t>
+          <t>pnl-dept</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>P&amp;L Spread</t>
+          <t>P&amp;L by Department</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -4856,18 +4856,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>allocation</t>
+          <t>pnl-spread</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Overhead Allocation</t>
+          <t>P&amp;L Spread</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4880,19 +4884,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr"/>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F7" s="11" t="inlineStr"/>
       <c r="G7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>allocation</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>P&amp;L Control</t>
+          <t>Overhead Allocation</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -4912,12 +4920,12 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>bva</t>
+          <t>control</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Budget vs Actual</t>
+          <t>P&amp;L Control</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -4930,23 +4938,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E9" s="11" t="inlineStr"/>
       <c r="F9" s="11" t="inlineStr"/>
       <c r="G9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>actions</t>
+          <t>bva</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Budget vs Actual</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -4970,12 +4974,12 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>forecast</t>
+          <t>actions</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Forecast</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -4993,22 +4997,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F11" s="11" t="inlineStr"/>
       <c r="G11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>forecast</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Cash Flow</t>
+          <t>Forecast</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -5026,18 +5026,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>rev-summary</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Revenue Summary</t>
+          <t>Cash Flow</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -5061,12 +5065,12 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>rev-schedule</t>
+          <t>rev-summary</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Revenue Schedule</t>
+          <t>Revenue Summary</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -5084,22 +5088,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F14" s="11" t="inlineStr"/>
       <c r="G14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>rev-forecast</t>
+          <t>rev-schedule</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Revenue Forecast</t>
+          <t>Revenue Schedule</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -5127,12 +5127,12 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>rev-forecast</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Revenue Forecast</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -5160,12 +5160,12 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>clients</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Top Clients</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5193,12 +5193,12 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>client-dept</t>
+          <t>clients</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Clients by Department</t>
+          <t>Top Clients</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -5216,18 +5216,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>client-dept</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Utilisation</t>
+          <t>Clients by Department</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -5245,22 +5249,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F19" s="11" t="inlineStr"/>
       <c r="G19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>profit-fte</t>
+          <t>util</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Profitability per FTE</t>
+          <t>Utilisation</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -5278,18 +5278,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr"/>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>staff-profit</t>
+          <t>profit-fte</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Profitability by Employee</t>
+          <t>Profitability per FTE</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -5313,12 +5317,12 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>staff-profit</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Detail Records</t>
+          <t>Profitability by Employee</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -5331,19 +5335,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr"/>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F22" s="11" t="inlineStr"/>
       <c r="G22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>charts</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Charts</t>
+          <t>Detail Records</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -5356,27 +5364,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E23" s="11" t="inlineStr"/>
+      <c r="F23" s="11" t="inlineStr"/>
       <c r="G23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>charts</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Charts</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -5389,19 +5389,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr"/>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>loaders</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Data Loaders</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -5421,12 +5429,12 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>loaders</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Data Loaders</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -5446,12 +5454,12 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -5471,12 +5479,12 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>config</t>
+          <t>distribution</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Config &amp; Variables</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -5496,12 +5504,12 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>access</t>
+          <t>config</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Config &amp; Variables</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -5509,7 +5517,11 @@
           <t>Always</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr"/>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E29" s="11" t="inlineStr"/>
       <c r="F29" s="11" t="inlineStr"/>
       <c r="G29" s="11" t="inlineStr"/>
@@ -5517,35 +5529,56 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr"/>
+      <c r="E30" s="11" t="inlineStr"/>
+      <c r="F30" s="11" t="inlineStr"/>
+      <c r="G30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
           <t>about</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>About</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/portal/templates/08 Config.xlsx
+++ b/portal/templates/08 Config.xlsx
@@ -4640,7 +4640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4804,12 +4804,12 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>pnl</t>
+          <t>story</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>P&amp;L</t>
+          <t>The Month</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -4827,18 +4827,26 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr"/>
-      <c r="G5" s="11" t="inlineStr"/>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>pnl-dept</t>
+          <t>pnl</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>P&amp;L by Department</t>
+          <t>P&amp;L</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -4856,22 +4864,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F6" s="11" t="inlineStr"/>
       <c r="G6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>pnl-spread</t>
+          <t>pnl-dept</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>P&amp;L Spread</t>
+          <t>P&amp;L by Department</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4889,18 +4893,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>allocation</t>
+          <t>pnl-spread</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Overhead Allocation</t>
+          <t>P&amp;L Spread</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -4913,19 +4921,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr"/>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F8" s="11" t="inlineStr"/>
       <c r="G8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>allocation</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>P&amp;L Control</t>
+          <t>Overhead Allocation</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -4945,12 +4957,12 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>bva</t>
+          <t>control</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Budget vs Actual</t>
+          <t>P&amp;L Control</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -4963,23 +4975,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E10" s="11" t="inlineStr"/>
       <c r="F10" s="11" t="inlineStr"/>
       <c r="G10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>actions</t>
+          <t>bva</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Budget vs Actual</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -5003,12 +5011,12 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>forecast</t>
+          <t>actions</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Forecast</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -5026,22 +5034,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F12" s="11" t="inlineStr"/>
       <c r="G12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>forecast</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Cash Flow</t>
+          <t>Forecast</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -5059,18 +5063,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr"/>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>rev-summary</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Revenue Summary</t>
+          <t>Cash Flow</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -5094,12 +5102,12 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>rev-schedule</t>
+          <t>rev-summary</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Revenue Schedule</t>
+          <t>Revenue Summary</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -5117,22 +5125,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F15" s="11" t="inlineStr"/>
       <c r="G15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>rev-forecast</t>
+          <t>rev-schedule</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Revenue Forecast</t>
+          <t>Revenue Schedule</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -5160,12 +5164,12 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>rev-forecast</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Revenue Forecast</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5193,12 +5197,12 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>clients</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Top Clients</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -5226,12 +5230,12 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>client-dept</t>
+          <t>clients</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Clients by Department</t>
+          <t>Top Clients</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -5249,18 +5253,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>client-dept</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Utilisation</t>
+          <t>Clients by Department</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -5278,22 +5286,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F20" s="11" t="inlineStr"/>
       <c r="G20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>profit-fte</t>
+          <t>util</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Profitability per FTE</t>
+          <t>Utilisation</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -5311,18 +5315,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr"/>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>staff-profit</t>
+          <t>profit-fte</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Profitability by Employee</t>
+          <t>Profitability per FTE</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -5346,12 +5354,12 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>staff-profit</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Detail Records</t>
+          <t>Profitability by Employee</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -5364,19 +5372,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr"/>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F23" s="11" t="inlineStr"/>
       <c r="G23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>charts</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Charts</t>
+          <t>Detail Records</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -5389,27 +5401,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E24" s="11" t="inlineStr"/>
+      <c r="F24" s="11" t="inlineStr"/>
       <c r="G24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>charts</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Charts</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -5422,19 +5426,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr"/>
-      <c r="F25" s="11" t="inlineStr"/>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>loaders</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Data Loaders</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -5454,12 +5466,12 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>loaders</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Data Loaders</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -5479,12 +5491,12 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -5504,12 +5516,12 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>config</t>
+          <t>distribution</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Config &amp; Variables</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -5529,12 +5541,12 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>access</t>
+          <t>config</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Config &amp; Variables</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -5542,7 +5554,11 @@
           <t>Always</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr"/>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E30" s="11" t="inlineStr"/>
       <c r="F30" s="11" t="inlineStr"/>
       <c r="G30" s="11" t="inlineStr"/>
@@ -5550,35 +5566,56 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr"/>
+      <c r="E31" s="11" t="inlineStr"/>
+      <c r="F31" s="11" t="inlineStr"/>
+      <c r="G31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
           <t>about</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>About</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5595,7 +5632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5604,6 +5641,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5637,9 +5675,14 @@
           <t>Note</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Tier 1 executive, tier 2 department head, tier 3 finance. Send: Yes or No. Addresses here are placeholders; replace them.</t>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Cadence</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 executive, tier 2 department head, tier 3 finance. Send: Yes or No. Cadence: Monthly, Fortnightly or Both. The list edited in the portal's Distribution page wins over this tab once published.</t>
         </is>
       </c>
     </row>
@@ -5668,6 +5711,11 @@
           <t>Full result, cost and margin, commentary</t>
         </is>
       </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -5690,6 +5738,11 @@
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr"/>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -5718,6 +5771,11 @@
       <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Own department in depth, one line on the rest</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -5746,6 +5804,11 @@
           <t>No address yet</t>
         </is>
       </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Fortnightly</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -5770,6 +5833,11 @@
       <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Finance: the controls and data quality</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -5780,6 +5848,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -5788,6 +5857,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -5796,6 +5866,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -5804,6 +5875,7 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -5812,6 +5884,7 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -5820,6 +5893,7 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -5828,6 +5902,7 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -5836,6 +5911,7 @@
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -5844,6 +5920,7 @@
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -5852,6 +5929,7 @@
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -5860,6 +5938,7 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -5868,6 +5947,7 @@
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -5876,6 +5956,7 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -5884,6 +5965,7 @@
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -5892,6 +5974,7 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -5900,6 +5983,7 @@
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -5908,6 +5992,7 @@
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -5916,6 +6001,7 @@
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -5924,6 +6010,7 @@
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -5932,6 +6019,7 @@
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -5940,6 +6028,7 @@
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -5948,6 +6037,7 @@
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -5956,6 +6046,7 @@
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -5964,6 +6055,7 @@
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -5972,6 +6064,7 @@
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -5980,6 +6073,7 @@
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -5988,6 +6082,7 @@
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -5996,6 +6091,7 @@
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -6004,6 +6100,7 @@
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -6012,6 +6109,7 @@
       <c r="D36" s="5" t="n"/>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -6020,6 +6118,7 @@
       <c r="D37" s="5" t="n"/>
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -6028,6 +6127,7 @@
       <c r="D38" s="5" t="n"/>
       <c r="E38" s="5" t="n"/>
       <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -6036,6 +6136,7 @@
       <c r="D39" s="5" t="n"/>
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -6044,6 +6145,7 @@
       <c r="D40" s="5" t="n"/>
       <c r="E40" s="5" t="n"/>
       <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -6052,6 +6154,7 @@
       <c r="D41" s="5" t="n"/>
       <c r="E41" s="5" t="n"/>
       <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -6060,6 +6163,7 @@
       <c r="D42" s="5" t="n"/>
       <c r="E42" s="5" t="n"/>
       <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -6068,6 +6172,7 @@
       <c r="D43" s="5" t="n"/>
       <c r="E43" s="5" t="n"/>
       <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -6076,6 +6181,7 @@
       <c r="D44" s="5" t="n"/>
       <c r="E44" s="5" t="n"/>
       <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -6084,6 +6190,7 @@
       <c r="D45" s="5" t="n"/>
       <c r="E45" s="5" t="n"/>
       <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -6092,6 +6199,7 @@
       <c r="D46" s="5" t="n"/>
       <c r="E46" s="5" t="n"/>
       <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -6100,6 +6208,7 @@
       <c r="D47" s="5" t="n"/>
       <c r="E47" s="5" t="n"/>
       <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -6108,6 +6217,7 @@
       <c r="D48" s="5" t="n"/>
       <c r="E48" s="5" t="n"/>
       <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -6116,6 +6226,7 @@
       <c r="D49" s="5" t="n"/>
       <c r="E49" s="5" t="n"/>
       <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -6124,6 +6235,7 @@
       <c r="D50" s="5" t="n"/>
       <c r="E50" s="5" t="n"/>
       <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -6132,6 +6244,7 @@
       <c r="D51" s="5" t="n"/>
       <c r="E51" s="5" t="n"/>
       <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -6140,6 +6253,7 @@
       <c r="D52" s="5" t="n"/>
       <c r="E52" s="5" t="n"/>
       <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -6148,6 +6262,7 @@
       <c r="D53" s="5" t="n"/>
       <c r="E53" s="5" t="n"/>
       <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -6156,6 +6271,7 @@
       <c r="D54" s="5" t="n"/>
       <c r="E54" s="5" t="n"/>
       <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -6164,6 +6280,7 @@
       <c r="D55" s="5" t="n"/>
       <c r="E55" s="5" t="n"/>
       <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -6172,6 +6289,7 @@
       <c r="D56" s="5" t="n"/>
       <c r="E56" s="5" t="n"/>
       <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -6180,6 +6298,7 @@
       <c r="D57" s="5" t="n"/>
       <c r="E57" s="5" t="n"/>
       <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -6188,6 +6307,7 @@
       <c r="D58" s="5" t="n"/>
       <c r="E58" s="5" t="n"/>
       <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -6196,6 +6316,7 @@
       <c r="D59" s="5" t="n"/>
       <c r="E59" s="5" t="n"/>
       <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
@@ -6204,6 +6325,7 @@
       <c r="D60" s="5" t="n"/>
       <c r="E60" s="5" t="n"/>
       <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n"/>
@@ -6212,6 +6334,7 @@
       <c r="D61" s="5" t="n"/>
       <c r="E61" s="5" t="n"/>
       <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -6220,6 +6343,7 @@
       <c r="D62" s="5" t="n"/>
       <c r="E62" s="5" t="n"/>
       <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -6228,6 +6352,7 @@
       <c r="D63" s="5" t="n"/>
       <c r="E63" s="5" t="n"/>
       <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
@@ -6236,6 +6361,7 @@
       <c r="D64" s="5" t="n"/>
       <c r="E64" s="5" t="n"/>
       <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
@@ -6244,6 +6370,7 @@
       <c r="D65" s="5" t="n"/>
       <c r="E65" s="5" t="n"/>
       <c r="F65" s="5" t="n"/>
+      <c r="G65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -6252,6 +6379,7 @@
       <c r="D66" s="5" t="n"/>
       <c r="E66" s="5" t="n"/>
       <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -6260,6 +6388,7 @@
       <c r="D67" s="5" t="n"/>
       <c r="E67" s="5" t="n"/>
       <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n"/>
@@ -6268,6 +6397,7 @@
       <c r="D68" s="5" t="n"/>
       <c r="E68" s="5" t="n"/>
       <c r="F68" s="5" t="n"/>
+      <c r="G68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
@@ -6276,6 +6406,7 @@
       <c r="D69" s="5" t="n"/>
       <c r="E69" s="5" t="n"/>
       <c r="F69" s="5" t="n"/>
+      <c r="G69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -6284,6 +6415,7 @@
       <c r="D70" s="5" t="n"/>
       <c r="E70" s="5" t="n"/>
       <c r="F70" s="5" t="n"/>
+      <c r="G70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -6292,6 +6424,7 @@
       <c r="D71" s="5" t="n"/>
       <c r="E71" s="5" t="n"/>
       <c r="F71" s="5" t="n"/>
+      <c r="G71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
@@ -6300,6 +6433,7 @@
       <c r="D72" s="5" t="n"/>
       <c r="E72" s="5" t="n"/>
       <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n"/>
@@ -6308,6 +6442,7 @@
       <c r="D73" s="5" t="n"/>
       <c r="E73" s="5" t="n"/>
       <c r="F73" s="5" t="n"/>
+      <c r="G73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -6316,6 +6451,7 @@
       <c r="D74" s="5" t="n"/>
       <c r="E74" s="5" t="n"/>
       <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -6324,6 +6460,7 @@
       <c r="D75" s="5" t="n"/>
       <c r="E75" s="5" t="n"/>
       <c r="F75" s="5" t="n"/>
+      <c r="G75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
@@ -6332,6 +6469,7 @@
       <c r="D76" s="5" t="n"/>
       <c r="E76" s="5" t="n"/>
       <c r="F76" s="5" t="n"/>
+      <c r="G76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
@@ -6340,6 +6478,7 @@
       <c r="D77" s="5" t="n"/>
       <c r="E77" s="5" t="n"/>
       <c r="F77" s="5" t="n"/>
+      <c r="G77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -6348,6 +6487,7 @@
       <c r="D78" s="5" t="n"/>
       <c r="E78" s="5" t="n"/>
       <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -6356,6 +6496,7 @@
       <c r="D79" s="5" t="n"/>
       <c r="E79" s="5" t="n"/>
       <c r="F79" s="5" t="n"/>
+      <c r="G79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n"/>
@@ -6364,6 +6505,7 @@
       <c r="D80" s="5" t="n"/>
       <c r="E80" s="5" t="n"/>
       <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
@@ -6372,6 +6514,7 @@
       <c r="D81" s="5" t="n"/>
       <c r="E81" s="5" t="n"/>
       <c r="F81" s="5" t="n"/>
+      <c r="G81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -6380,6 +6523,7 @@
       <c r="D82" s="5" t="n"/>
       <c r="E82" s="5" t="n"/>
       <c r="F82" s="5" t="n"/>
+      <c r="G82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -6388,6 +6532,7 @@
       <c r="D83" s="5" t="n"/>
       <c r="E83" s="5" t="n"/>
       <c r="F83" s="5" t="n"/>
+      <c r="G83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
@@ -6396,6 +6541,7 @@
       <c r="D84" s="5" t="n"/>
       <c r="E84" s="5" t="n"/>
       <c r="F84" s="5" t="n"/>
+      <c r="G84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
@@ -6404,6 +6550,7 @@
       <c r="D85" s="5" t="n"/>
       <c r="E85" s="5" t="n"/>
       <c r="F85" s="5" t="n"/>
+      <c r="G85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
@@ -6412,6 +6559,7 @@
       <c r="D86" s="5" t="n"/>
       <c r="E86" s="5" t="n"/>
       <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
@@ -6420,6 +6568,7 @@
       <c r="D87" s="5" t="n"/>
       <c r="E87" s="5" t="n"/>
       <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n"/>
@@ -6428,6 +6577,7 @@
       <c r="D88" s="5" t="n"/>
       <c r="E88" s="5" t="n"/>
       <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n"/>
@@ -6436,6 +6586,7 @@
       <c r="D89" s="5" t="n"/>
       <c r="E89" s="5" t="n"/>
       <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n"/>
@@ -6444,6 +6595,7 @@
       <c r="D90" s="5" t="n"/>
       <c r="E90" s="5" t="n"/>
       <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n"/>
@@ -6452,6 +6604,7 @@
       <c r="D91" s="5" t="n"/>
       <c r="E91" s="5" t="n"/>
       <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n"/>
@@ -6460,6 +6613,7 @@
       <c r="D92" s="5" t="n"/>
       <c r="E92" s="5" t="n"/>
       <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
@@ -6468,6 +6622,7 @@
       <c r="D93" s="5" t="n"/>
       <c r="E93" s="5" t="n"/>
       <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n"/>
@@ -6476,6 +6631,7 @@
       <c r="D94" s="5" t="n"/>
       <c r="E94" s="5" t="n"/>
       <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
@@ -6484,6 +6640,7 @@
       <c r="D95" s="5" t="n"/>
       <c r="E95" s="5" t="n"/>
       <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n"/>
@@ -6492,6 +6649,7 @@
       <c r="D96" s="5" t="n"/>
       <c r="E96" s="5" t="n"/>
       <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
@@ -6500,6 +6658,7 @@
       <c r="D97" s="5" t="n"/>
       <c r="E97" s="5" t="n"/>
       <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
@@ -6508,6 +6667,7 @@
       <c r="D98" s="5" t="n"/>
       <c r="E98" s="5" t="n"/>
       <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
@@ -6516,6 +6676,7 @@
       <c r="D99" s="5" t="n"/>
       <c r="E99" s="5" t="n"/>
       <c r="F99" s="5" t="n"/>
+      <c r="G99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n"/>
@@ -6524,6 +6685,7 @@
       <c r="D100" s="5" t="n"/>
       <c r="E100" s="5" t="n"/>
       <c r="F100" s="5" t="n"/>
+      <c r="G100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n"/>
@@ -6532,6 +6694,7 @@
       <c r="D101" s="5" t="n"/>
       <c r="E101" s="5" t="n"/>
       <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n"/>
@@ -6540,6 +6703,7 @@
       <c r="D102" s="5" t="n"/>
       <c r="E102" s="5" t="n"/>
       <c r="F102" s="5" t="n"/>
+      <c r="G102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n"/>
@@ -6548,6 +6712,7 @@
       <c r="D103" s="5" t="n"/>
       <c r="E103" s="5" t="n"/>
       <c r="F103" s="5" t="n"/>
+      <c r="G103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n"/>
@@ -6556,6 +6721,7 @@
       <c r="D104" s="5" t="n"/>
       <c r="E104" s="5" t="n"/>
       <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n"/>
@@ -6564,6 +6730,7 @@
       <c r="D105" s="5" t="n"/>
       <c r="E105" s="5" t="n"/>
       <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n"/>
@@ -6572,6 +6739,7 @@
       <c r="D106" s="5" t="n"/>
       <c r="E106" s="5" t="n"/>
       <c r="F106" s="5" t="n"/>
+      <c r="G106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
@@ -6580,6 +6748,7 @@
       <c r="D107" s="5" t="n"/>
       <c r="E107" s="5" t="n"/>
       <c r="F107" s="5" t="n"/>
+      <c r="G107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n"/>
@@ -6588,6 +6757,7 @@
       <c r="D108" s="5" t="n"/>
       <c r="E108" s="5" t="n"/>
       <c r="F108" s="5" t="n"/>
+      <c r="G108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n"/>
@@ -6596,6 +6766,7 @@
       <c r="D109" s="5" t="n"/>
       <c r="E109" s="5" t="n"/>
       <c r="F109" s="5" t="n"/>
+      <c r="G109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n"/>
@@ -6604,6 +6775,7 @@
       <c r="D110" s="5" t="n"/>
       <c r="E110" s="5" t="n"/>
       <c r="F110" s="5" t="n"/>
+      <c r="G110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n"/>
@@ -6612,6 +6784,7 @@
       <c r="D111" s="5" t="n"/>
       <c r="E111" s="5" t="n"/>
       <c r="F111" s="5" t="n"/>
+      <c r="G111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n"/>
@@ -6620,6 +6793,7 @@
       <c r="D112" s="5" t="n"/>
       <c r="E112" s="5" t="n"/>
       <c r="F112" s="5" t="n"/>
+      <c r="G112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n"/>
@@ -6628,6 +6802,7 @@
       <c r="D113" s="5" t="n"/>
       <c r="E113" s="5" t="n"/>
       <c r="F113" s="5" t="n"/>
+      <c r="G113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n"/>
@@ -6636,6 +6811,7 @@
       <c r="D114" s="5" t="n"/>
       <c r="E114" s="5" t="n"/>
       <c r="F114" s="5" t="n"/>
+      <c r="G114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n"/>
@@ -6644,6 +6820,7 @@
       <c r="D115" s="5" t="n"/>
       <c r="E115" s="5" t="n"/>
       <c r="F115" s="5" t="n"/>
+      <c r="G115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n"/>
@@ -6652,6 +6829,7 @@
       <c r="D116" s="5" t="n"/>
       <c r="E116" s="5" t="n"/>
       <c r="F116" s="5" t="n"/>
+      <c r="G116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n"/>
@@ -6660,6 +6838,7 @@
       <c r="D117" s="5" t="n"/>
       <c r="E117" s="5" t="n"/>
       <c r="F117" s="5" t="n"/>
+      <c r="G117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n"/>
@@ -6668,6 +6847,7 @@
       <c r="D118" s="5" t="n"/>
       <c r="E118" s="5" t="n"/>
       <c r="F118" s="5" t="n"/>
+      <c r="G118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n"/>
@@ -6676,6 +6856,7 @@
       <c r="D119" s="5" t="n"/>
       <c r="E119" s="5" t="n"/>
       <c r="F119" s="5" t="n"/>
+      <c r="G119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n"/>
@@ -6684,6 +6865,7 @@
       <c r="D120" s="5" t="n"/>
       <c r="E120" s="5" t="n"/>
       <c r="F120" s="5" t="n"/>
+      <c r="G120" s="5" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n"/>
@@ -6692,6 +6874,7 @@
       <c r="D121" s="5" t="n"/>
       <c r="E121" s="5" t="n"/>
       <c r="F121" s="5" t="n"/>
+      <c r="G121" s="5" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n"/>
@@ -6700,6 +6883,7 @@
       <c r="D122" s="5" t="n"/>
       <c r="E122" s="5" t="n"/>
       <c r="F122" s="5" t="n"/>
+      <c r="G122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n"/>
@@ -6708,6 +6892,7 @@
       <c r="D123" s="5" t="n"/>
       <c r="E123" s="5" t="n"/>
       <c r="F123" s="5" t="n"/>
+      <c r="G123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n"/>
@@ -6716,6 +6901,7 @@
       <c r="D124" s="5" t="n"/>
       <c r="E124" s="5" t="n"/>
       <c r="F124" s="5" t="n"/>
+      <c r="G124" s="5" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n"/>
@@ -6724,6 +6910,7 @@
       <c r="D125" s="5" t="n"/>
       <c r="E125" s="5" t="n"/>
       <c r="F125" s="5" t="n"/>
+      <c r="G125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n"/>
@@ -6732,6 +6919,7 @@
       <c r="D126" s="5" t="n"/>
       <c r="E126" s="5" t="n"/>
       <c r="F126" s="5" t="n"/>
+      <c r="G126" s="5" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n"/>
@@ -6740,6 +6928,7 @@
       <c r="D127" s="5" t="n"/>
       <c r="E127" s="5" t="n"/>
       <c r="F127" s="5" t="n"/>
+      <c r="G127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n"/>
@@ -6748,6 +6937,7 @@
       <c r="D128" s="5" t="n"/>
       <c r="E128" s="5" t="n"/>
       <c r="F128" s="5" t="n"/>
+      <c r="G128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n"/>
@@ -6756,6 +6946,7 @@
       <c r="D129" s="5" t="n"/>
       <c r="E129" s="5" t="n"/>
       <c r="F129" s="5" t="n"/>
+      <c r="G129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n"/>
@@ -6764,6 +6955,7 @@
       <c r="D130" s="5" t="n"/>
       <c r="E130" s="5" t="n"/>
       <c r="F130" s="5" t="n"/>
+      <c r="G130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n"/>
@@ -6772,6 +6964,7 @@
       <c r="D131" s="5" t="n"/>
       <c r="E131" s="5" t="n"/>
       <c r="F131" s="5" t="n"/>
+      <c r="G131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n"/>
@@ -6780,6 +6973,7 @@
       <c r="D132" s="5" t="n"/>
       <c r="E132" s="5" t="n"/>
       <c r="F132" s="5" t="n"/>
+      <c r="G132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n"/>
@@ -6788,6 +6982,7 @@
       <c r="D133" s="5" t="n"/>
       <c r="E133" s="5" t="n"/>
       <c r="F133" s="5" t="n"/>
+      <c r="G133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n"/>
@@ -6796,6 +6991,7 @@
       <c r="D134" s="5" t="n"/>
       <c r="E134" s="5" t="n"/>
       <c r="F134" s="5" t="n"/>
+      <c r="G134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n"/>
@@ -6804,6 +7000,7 @@
       <c r="D135" s="5" t="n"/>
       <c r="E135" s="5" t="n"/>
       <c r="F135" s="5" t="n"/>
+      <c r="G135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n"/>
@@ -6812,6 +7009,7 @@
       <c r="D136" s="5" t="n"/>
       <c r="E136" s="5" t="n"/>
       <c r="F136" s="5" t="n"/>
+      <c r="G136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n"/>
@@ -6820,6 +7018,7 @@
       <c r="D137" s="5" t="n"/>
       <c r="E137" s="5" t="n"/>
       <c r="F137" s="5" t="n"/>
+      <c r="G137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n"/>
@@ -6828,6 +7027,7 @@
       <c r="D138" s="5" t="n"/>
       <c r="E138" s="5" t="n"/>
       <c r="F138" s="5" t="n"/>
+      <c r="G138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n"/>
@@ -6836,6 +7036,7 @@
       <c r="D139" s="5" t="n"/>
       <c r="E139" s="5" t="n"/>
       <c r="F139" s="5" t="n"/>
+      <c r="G139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n"/>
@@ -6844,6 +7045,7 @@
       <c r="D140" s="5" t="n"/>
       <c r="E140" s="5" t="n"/>
       <c r="F140" s="5" t="n"/>
+      <c r="G140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n"/>
@@ -6852,6 +7054,7 @@
       <c r="D141" s="5" t="n"/>
       <c r="E141" s="5" t="n"/>
       <c r="F141" s="5" t="n"/>
+      <c r="G141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n"/>
@@ -6860,6 +7063,7 @@
       <c r="D142" s="5" t="n"/>
       <c r="E142" s="5" t="n"/>
       <c r="F142" s="5" t="n"/>
+      <c r="G142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n"/>
@@ -6868,6 +7072,7 @@
       <c r="D143" s="5" t="n"/>
       <c r="E143" s="5" t="n"/>
       <c r="F143" s="5" t="n"/>
+      <c r="G143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n"/>
@@ -6876,6 +7081,7 @@
       <c r="D144" s="5" t="n"/>
       <c r="E144" s="5" t="n"/>
       <c r="F144" s="5" t="n"/>
+      <c r="G144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n"/>
@@ -6884,6 +7090,7 @@
       <c r="D145" s="5" t="n"/>
       <c r="E145" s="5" t="n"/>
       <c r="F145" s="5" t="n"/>
+      <c r="G145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n"/>
@@ -6892,6 +7099,7 @@
       <c r="D146" s="5" t="n"/>
       <c r="E146" s="5" t="n"/>
       <c r="F146" s="5" t="n"/>
+      <c r="G146" s="5" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n"/>
@@ -6900,6 +7108,7 @@
       <c r="D147" s="5" t="n"/>
       <c r="E147" s="5" t="n"/>
       <c r="F147" s="5" t="n"/>
+      <c r="G147" s="5" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n"/>
@@ -6908,6 +7117,7 @@
       <c r="D148" s="5" t="n"/>
       <c r="E148" s="5" t="n"/>
       <c r="F148" s="5" t="n"/>
+      <c r="G148" s="5" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n"/>
@@ -6916,6 +7126,7 @@
       <c r="D149" s="5" t="n"/>
       <c r="E149" s="5" t="n"/>
       <c r="F149" s="5" t="n"/>
+      <c r="G149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n"/>
@@ -6924,6 +7135,7 @@
       <c r="D150" s="5" t="n"/>
       <c r="E150" s="5" t="n"/>
       <c r="F150" s="5" t="n"/>
+      <c r="G150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n"/>
@@ -6932,6 +7144,7 @@
       <c r="D151" s="5" t="n"/>
       <c r="E151" s="5" t="n"/>
       <c r="F151" s="5" t="n"/>
+      <c r="G151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n"/>
@@ -6940,6 +7153,7 @@
       <c r="D152" s="5" t="n"/>
       <c r="E152" s="5" t="n"/>
       <c r="F152" s="5" t="n"/>
+      <c r="G152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n"/>
@@ -6948,6 +7162,7 @@
       <c r="D153" s="5" t="n"/>
       <c r="E153" s="5" t="n"/>
       <c r="F153" s="5" t="n"/>
+      <c r="G153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n"/>
@@ -6956,6 +7171,7 @@
       <c r="D154" s="5" t="n"/>
       <c r="E154" s="5" t="n"/>
       <c r="F154" s="5" t="n"/>
+      <c r="G154" s="5" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n"/>
@@ -6964,6 +7180,7 @@
       <c r="D155" s="5" t="n"/>
       <c r="E155" s="5" t="n"/>
       <c r="F155" s="5" t="n"/>
+      <c r="G155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n"/>
@@ -6972,6 +7189,7 @@
       <c r="D156" s="5" t="n"/>
       <c r="E156" s="5" t="n"/>
       <c r="F156" s="5" t="n"/>
+      <c r="G156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n"/>
@@ -6980,6 +7198,7 @@
       <c r="D157" s="5" t="n"/>
       <c r="E157" s="5" t="n"/>
       <c r="F157" s="5" t="n"/>
+      <c r="G157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n"/>
@@ -6988,6 +7207,7 @@
       <c r="D158" s="5" t="n"/>
       <c r="E158" s="5" t="n"/>
       <c r="F158" s="5" t="n"/>
+      <c r="G158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n"/>
@@ -6996,6 +7216,7 @@
       <c r="D159" s="5" t="n"/>
       <c r="E159" s="5" t="n"/>
       <c r="F159" s="5" t="n"/>
+      <c r="G159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n"/>
@@ -7004,6 +7225,7 @@
       <c r="D160" s="5" t="n"/>
       <c r="E160" s="5" t="n"/>
       <c r="F160" s="5" t="n"/>
+      <c r="G160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n"/>
@@ -7012,6 +7234,7 @@
       <c r="D161" s="5" t="n"/>
       <c r="E161" s="5" t="n"/>
       <c r="F161" s="5" t="n"/>
+      <c r="G161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n"/>
@@ -7020,6 +7243,7 @@
       <c r="D162" s="5" t="n"/>
       <c r="E162" s="5" t="n"/>
       <c r="F162" s="5" t="n"/>
+      <c r="G162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n"/>
@@ -7028,6 +7252,7 @@
       <c r="D163" s="5" t="n"/>
       <c r="E163" s="5" t="n"/>
       <c r="F163" s="5" t="n"/>
+      <c r="G163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n"/>
@@ -7036,6 +7261,7 @@
       <c r="D164" s="5" t="n"/>
       <c r="E164" s="5" t="n"/>
       <c r="F164" s="5" t="n"/>
+      <c r="G164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n"/>
@@ -7044,6 +7270,7 @@
       <c r="D165" s="5" t="n"/>
       <c r="E165" s="5" t="n"/>
       <c r="F165" s="5" t="n"/>
+      <c r="G165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n"/>
@@ -7052,6 +7279,7 @@
       <c r="D166" s="5" t="n"/>
       <c r="E166" s="5" t="n"/>
       <c r="F166" s="5" t="n"/>
+      <c r="G166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n"/>
@@ -7060,6 +7288,7 @@
       <c r="D167" s="5" t="n"/>
       <c r="E167" s="5" t="n"/>
       <c r="F167" s="5" t="n"/>
+      <c r="G167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n"/>
@@ -7068,6 +7297,7 @@
       <c r="D168" s="5" t="n"/>
       <c r="E168" s="5" t="n"/>
       <c r="F168" s="5" t="n"/>
+      <c r="G168" s="5" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n"/>
@@ -7076,6 +7306,7 @@
       <c r="D169" s="5" t="n"/>
       <c r="E169" s="5" t="n"/>
       <c r="F169" s="5" t="n"/>
+      <c r="G169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n"/>
@@ -7084,6 +7315,7 @@
       <c r="D170" s="5" t="n"/>
       <c r="E170" s="5" t="n"/>
       <c r="F170" s="5" t="n"/>
+      <c r="G170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n"/>
@@ -7092,6 +7324,7 @@
       <c r="D171" s="5" t="n"/>
       <c r="E171" s="5" t="n"/>
       <c r="F171" s="5" t="n"/>
+      <c r="G171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n"/>
@@ -7100,6 +7333,7 @@
       <c r="D172" s="5" t="n"/>
       <c r="E172" s="5" t="n"/>
       <c r="F172" s="5" t="n"/>
+      <c r="G172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="n"/>
@@ -7108,6 +7342,7 @@
       <c r="D173" s="5" t="n"/>
       <c r="E173" s="5" t="n"/>
       <c r="F173" s="5" t="n"/>
+      <c r="G173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n"/>
@@ -7116,6 +7351,7 @@
       <c r="D174" s="5" t="n"/>
       <c r="E174" s="5" t="n"/>
       <c r="F174" s="5" t="n"/>
+      <c r="G174" s="5" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n"/>
@@ -7124,6 +7360,7 @@
       <c r="D175" s="5" t="n"/>
       <c r="E175" s="5" t="n"/>
       <c r="F175" s="5" t="n"/>
+      <c r="G175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n"/>
@@ -7132,6 +7369,7 @@
       <c r="D176" s="5" t="n"/>
       <c r="E176" s="5" t="n"/>
       <c r="F176" s="5" t="n"/>
+      <c r="G176" s="5" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n"/>
@@ -7140,6 +7378,7 @@
       <c r="D177" s="5" t="n"/>
       <c r="E177" s="5" t="n"/>
       <c r="F177" s="5" t="n"/>
+      <c r="G177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n"/>
@@ -7148,6 +7387,7 @@
       <c r="D178" s="5" t="n"/>
       <c r="E178" s="5" t="n"/>
       <c r="F178" s="5" t="n"/>
+      <c r="G178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n"/>
@@ -7156,6 +7396,7 @@
       <c r="D179" s="5" t="n"/>
       <c r="E179" s="5" t="n"/>
       <c r="F179" s="5" t="n"/>
+      <c r="G179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
@@ -7164,6 +7405,7 @@
       <c r="D180" s="5" t="n"/>
       <c r="E180" s="5" t="n"/>
       <c r="F180" s="5" t="n"/>
+      <c r="G180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n"/>
@@ -7172,6 +7414,7 @@
       <c r="D181" s="5" t="n"/>
       <c r="E181" s="5" t="n"/>
       <c r="F181" s="5" t="n"/>
+      <c r="G181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n"/>
@@ -7180,6 +7423,7 @@
       <c r="D182" s="5" t="n"/>
       <c r="E182" s="5" t="n"/>
       <c r="F182" s="5" t="n"/>
+      <c r="G182" s="5" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
@@ -7188,6 +7432,7 @@
       <c r="D183" s="5" t="n"/>
       <c r="E183" s="5" t="n"/>
       <c r="F183" s="5" t="n"/>
+      <c r="G183" s="5" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
@@ -7196,6 +7441,7 @@
       <c r="D184" s="5" t="n"/>
       <c r="E184" s="5" t="n"/>
       <c r="F184" s="5" t="n"/>
+      <c r="G184" s="5" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n"/>
@@ -7204,6 +7450,7 @@
       <c r="D185" s="5" t="n"/>
       <c r="E185" s="5" t="n"/>
       <c r="F185" s="5" t="n"/>
+      <c r="G185" s="5" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n"/>
@@ -7212,6 +7459,7 @@
       <c r="D186" s="5" t="n"/>
       <c r="E186" s="5" t="n"/>
       <c r="F186" s="5" t="n"/>
+      <c r="G186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n"/>
@@ -7220,6 +7468,7 @@
       <c r="D187" s="5" t="n"/>
       <c r="E187" s="5" t="n"/>
       <c r="F187" s="5" t="n"/>
+      <c r="G187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n"/>
@@ -7228,6 +7477,7 @@
       <c r="D188" s="5" t="n"/>
       <c r="E188" s="5" t="n"/>
       <c r="F188" s="5" t="n"/>
+      <c r="G188" s="5" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n"/>
@@ -7236,6 +7486,7 @@
       <c r="D189" s="5" t="n"/>
       <c r="E189" s="5" t="n"/>
       <c r="F189" s="5" t="n"/>
+      <c r="G189" s="5" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
@@ -7244,6 +7495,7 @@
       <c r="D190" s="5" t="n"/>
       <c r="E190" s="5" t="n"/>
       <c r="F190" s="5" t="n"/>
+      <c r="G190" s="5" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n"/>
@@ -7252,6 +7504,7 @@
       <c r="D191" s="5" t="n"/>
       <c r="E191" s="5" t="n"/>
       <c r="F191" s="5" t="n"/>
+      <c r="G191" s="5" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="n"/>
@@ -7260,6 +7513,7 @@
       <c r="D192" s="5" t="n"/>
       <c r="E192" s="5" t="n"/>
       <c r="F192" s="5" t="n"/>
+      <c r="G192" s="5" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
@@ -7268,6 +7522,7 @@
       <c r="D193" s="5" t="n"/>
       <c r="E193" s="5" t="n"/>
       <c r="F193" s="5" t="n"/>
+      <c r="G193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n"/>
@@ -7276,6 +7531,7 @@
       <c r="D194" s="5" t="n"/>
       <c r="E194" s="5" t="n"/>
       <c r="F194" s="5" t="n"/>
+      <c r="G194" s="5" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n"/>
@@ -7284,6 +7540,7 @@
       <c r="D195" s="5" t="n"/>
       <c r="E195" s="5" t="n"/>
       <c r="F195" s="5" t="n"/>
+      <c r="G195" s="5" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n"/>
@@ -7292,6 +7549,7 @@
       <c r="D196" s="5" t="n"/>
       <c r="E196" s="5" t="n"/>
       <c r="F196" s="5" t="n"/>
+      <c r="G196" s="5" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n"/>
@@ -7300,6 +7558,7 @@
       <c r="D197" s="5" t="n"/>
       <c r="E197" s="5" t="n"/>
       <c r="F197" s="5" t="n"/>
+      <c r="G197" s="5" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="n"/>
@@ -7308,6 +7567,7 @@
       <c r="D198" s="5" t="n"/>
       <c r="E198" s="5" t="n"/>
       <c r="F198" s="5" t="n"/>
+      <c r="G198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n"/>
@@ -7316,6 +7576,7 @@
       <c r="D199" s="5" t="n"/>
       <c r="E199" s="5" t="n"/>
       <c r="F199" s="5" t="n"/>
+      <c r="G199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n"/>
@@ -7324,6 +7585,7 @@
       <c r="D200" s="5" t="n"/>
       <c r="E200" s="5" t="n"/>
       <c r="F200" s="5" t="n"/>
+      <c r="G200" s="5" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n"/>
@@ -7332,11 +7594,15 @@
       <c r="D201" s="5" t="n"/>
       <c r="E201" s="5" t="n"/>
       <c r="F201" s="5" t="n"/>
+      <c r="G201" s="5" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Monthly,Fortnightly,Both"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/portal/templates/08 Config.xlsx
+++ b/portal/templates/08 Config.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -768,15 +768,28 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
+          <t>Portal link</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Where people open the portal: the SharePoint link to CTS Business Intelligence Portal.html, or the synced folder path. Goes in every email</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
           <t>Portal version</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>2.0.0</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4640,7 +4653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5413,7 +5426,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Charts</t>
+          <t>Trends</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -5466,12 +5479,12 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>loaders</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Data Loaders</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -5491,12 +5504,12 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>distribution</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -5516,12 +5529,12 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>config</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Config &amp; Variables</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -5541,12 +5554,12 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>config</t>
+          <t>access</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Config &amp; Variables</t>
+          <t>Access Control</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -5554,11 +5567,7 @@
           <t>Always</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="D30" s="11" t="inlineStr"/>
       <c r="E30" s="11" t="inlineStr"/>
       <c r="F30" s="11" t="inlineStr"/>
       <c r="G30" s="11" t="inlineStr"/>
@@ -5566,12 +5575,12 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>access</t>
+          <t>about</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>About</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -5579,43 +5588,22 @@
           <t>Always</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr"/>
-      <c r="E31" s="11" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr"/>
-      <c r="G31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>about</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>About</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/portal/templates/08 Config.xlsx
+++ b/portal/templates/08 Config.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Reporting" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Departments" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Split bases" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Split assignment" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Holidays" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Users" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Tabs by role" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Distribution" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporting" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departments" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Split bases" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Split assignment" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holidays" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabs by role" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribution" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4653,7 +4653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4995,12 +4995,12 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>bva</t>
+          <t>checks</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Budget vs Actual</t>
+          <t>Controller Checks</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -5013,23 +5013,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E11" s="11" t="inlineStr"/>
       <c r="F11" s="11" t="inlineStr"/>
       <c r="G11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>actions</t>
+          <t>bva</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Budget vs Actual</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -5053,12 +5049,12 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>forecast</t>
+          <t>actions</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Forecast</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -5076,22 +5072,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F13" s="11" t="inlineStr"/>
       <c r="G13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>forecast</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Cash Flow</t>
+          <t>Forecast</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -5109,18 +5101,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>rev-summary</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Revenue Summary</t>
+          <t>Cash Flow</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -5144,12 +5140,12 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>rev-schedule</t>
+          <t>rev-summary</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Revenue Schedule</t>
+          <t>Revenue Summary</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -5167,22 +5163,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F16" s="11" t="inlineStr"/>
       <c r="G16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>rev-forecast</t>
+          <t>rev-schedule</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Revenue Forecast</t>
+          <t>Revenue Schedule</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -5210,12 +5202,12 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>rev-forecast</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Pipeline</t>
+          <t>Revenue Forecast</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -5243,12 +5235,12 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>clients</t>
+          <t>rev-risk</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Top Clients</t>
+          <t>Revenue Risk</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -5276,12 +5268,12 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>client-dept</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Clients by Department</t>
+          <t>Pipeline</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -5299,18 +5291,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr"/>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>clients</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Utilisation</t>
+          <t>Top Clients</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -5338,12 +5334,12 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>profit-fte</t>
+          <t>client-dept</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Profitability per FTE</t>
+          <t>Clients by Department</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -5367,12 +5363,12 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>staff-profit</t>
+          <t>util</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Profitability by Employee</t>
+          <t>Utilisation</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -5390,18 +5386,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr"/>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>profit-fte</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Detail Records</t>
+          <t>Profitability per FTE</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -5414,19 +5414,23 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr"/>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="F24" s="11" t="inlineStr"/>
       <c r="G24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>charts</t>
+          <t>staff-profit</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Trends</t>
+          <t>Profitability by Employee</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -5444,22 +5448,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F25" s="11" t="inlineStr"/>
       <c r="G25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>setup</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Detail Records</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -5479,12 +5479,12 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>charts</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Trends</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -5497,19 +5497,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr"/>
-      <c r="F27" s="11" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>distribution</t>
+          <t>setup</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -5529,12 +5537,12 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>config</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Config &amp; Variables</t>
+          <t>Build</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -5554,12 +5562,12 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>access</t>
+          <t>distribution</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Distribution</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -5567,7 +5575,11 @@
           <t>Always</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr"/>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E30" s="11" t="inlineStr"/>
       <c r="F30" s="11" t="inlineStr"/>
       <c r="G30" s="11" t="inlineStr"/>
@@ -5575,35 +5587,81 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Config &amp; Variables</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr"/>
+      <c r="F31" s="11" t="inlineStr"/>
+      <c r="G31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>access</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr"/>
+      <c r="E32" s="11" t="inlineStr"/>
+      <c r="F32" s="11" t="inlineStr"/>
+      <c r="G32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
           <t>about</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>About</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
